--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2500_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2500_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA2"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -845,7 +845,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Air-Way FF2500 (s20, double-pass 2026-10-15, parts.air-way.com/api/series/20, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p7 FS2500-08-08-FG (ORFS-p007-t05); FORGED part: Air-Way NON-forged row FF2500-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length = gen_straight2 FSM_MEAS (Brennan FS2403-08-08); on the forged legs the thread major runs to the end length and steps down to the hex flats (Brennan FS6500 / FS6801 / FS2701-08 forged legs) - the end stands proud of the flats; hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF2500 (s20, double-pass 2026-10-15, parts.air-way.com/api/series/20, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p7 FS2500-08-08-FG (ORFS-p007-t05); FORGED part: Air-Way NON-forged row FF2500-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -856,6 +856,730 @@
       <c r="BA2" t="inlineStr">
         <is>
           <t>FS2500-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS2500-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="F3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="O3" t="n">
+        <v>45</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>FS2500-06-06-FG</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Elbow (male face seal x male face seal), 11/16-16 UN (male O-ring face seal, SAE J1453) x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>FS2500</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Air-Way FF2500 (s20, double-pass 2026-10-15, parts.air-way.com/api/series/20, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p7 FS2500-06-06-FG (ORFS-p007-t05); FORGED part: Air-Way NON-forged row FF2500-6-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2500-6-6-O = Brennan forged FS2500-06-06-FG p7 on every compared cell (M1 LGTH ~ L7 (1), M2 LGTH ~ L7 (2), JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2500 is used only where Brennan FS2500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5349 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>FS2500-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS2500-10-10-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="O4" t="n">
+        <v>45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.61149</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>FS2500-10-10-FG</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Elbow (male face seal x male face seal), 1-14 UN (male O-ring face seal, SAE J1453) x 1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>FS2500</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Air-Way FF2500 (s20, double-pass 2026-10-15, parts.air-way.com/api/series/20, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p7 FS2500-10-10-FG (ORFS-p007-t05); FORGED part: Air-Way NON-forged row FF2500-10-10-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2500-10-10-O = Brennan forged FS2500-10-10-FG p7 on every compared cell (M1 LGTH ~ L7 (1), M2 LGTH ~ L7 (2), JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2500 is used only where Brennan FS2500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5353 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>FS2500-10-10-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FS2500-20-16-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.62675</v>
+      </c>
+      <c r="O5" t="n">
+        <v>45</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.6565</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5335</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.62675</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>FS2500-20-16-FG</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Elbow (male face seal x male face seal), 1 11/16-12 UN (male O-ring face seal, SAE J1453) x 1 7/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>FS2500</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>1 7/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7_1@DRIVE: Brennan ORFS catalog p7 table ORFS-p007-t05 "FS2500-FG MFS-MFS 90 DEG ELBOW" row FS2500-20-16-FG col "M1 LGTH" = "1.76" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 471.3, page verified True) [Brennan = yes 2026-10-18] - leg 1 (A1) face -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; L7_2@DRIVE: Brennan ORFS catalog p7 table ORFS-p007-t05 "FS2500-FG MFS-MFS 90 DEG ELBOW" row FS2500-20-16-FG col "M2 LGTH" = "1.76" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 471.3, page verified True) [Brennan = yes 2026-10-18] - leg 2 (A2) face -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p7 table ORFS-p007-t05 "FS2500-FG MFS-MFS 90 DEG ELBOW" row FS2500-20-16-FG col "JJ FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 471.3, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -20 = 1.6875 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "A1 THREAD" "1-11/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -16 = 1.4375 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "A2 THREAD" "1-7/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p7 table ORFS-p007-t05 "FS2500-FG MFS-MFS 90 DEG ELBOW" row FS2500-20-16-FG col "A1 THREAD" "1-11/16-12" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p7 table ORFS-p007-t05 "FS2500-FG MFS-MFS 90 DEG ELBOW" row FS2500-20-16-FG col "A2 THREAD" "1-7/16-12" in the table's format; D1_1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2500: FSM -20 bore on 2 Air-Way row(s): 1.02 (unanimous) [Air-Way, not Brennan]; D1_2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2500: FSM -16 bore on 2 Air-Way row(s): 0.81 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>forged (-FG): Brennan p7 prints it but Air-Way has no non-forged row - Brennan-only stays MISSING | forged (-FG): the Air-Way NON-forged series FF2500 is used only where Brennan FS2500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5358 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p7 FS2500-20-16-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>FS2500-20-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FS2500-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="O6" t="n">
+        <v>45</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.94058</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>FS2500-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Elbow (male face seal x male face seal), 1 11/16-12 UN (male O-ring face seal, SAE J1453) x 1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>FS2500</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Air-Way FF2500 (s20, double-pass 2026-10-15, parts.air-way.com/api/series/20, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p7 FS2500-20-20-FG (ORFS-p007-t05); FORGED part: Air-Way NON-forged row FF2500-20-20-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2500-20-20-O = Brennan forged FS2500-20-20-FG p7 on every compared cell (M1 LGTH ~ L7 (1), M2 LGTH ~ L7 (2), JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2500 is used only where Brennan FS2500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5359 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>FS2500-20-20-FG</t>
         </is>
       </c>
     </row>

--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2500_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2500_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
